--- a/Data/EC/NIT-9009517303.xlsx
+++ b/Data/EC/NIT-9009517303.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D19BC73-9FDA-4915-B53E-1215EBC93867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEB209C7-9368-41B8-B036-D86C8D9F0127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1984E2F5-6560-4DA4-A16A-6CE684B7192B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{369C0131-7084-4384-9719-FD1C9BB2457A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="90">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -65,196 +65,214 @@
     <t>CC</t>
   </si>
   <si>
+    <t>1047398708</t>
+  </si>
+  <si>
+    <t>ISAIAS MORELO LARA</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>9299657</t>
+  </si>
+  <si>
+    <t>ORLANDO MARRIAGA MARTINEZ</t>
+  </si>
+  <si>
+    <t>2501</t>
+  </si>
+  <si>
+    <t>2412</t>
+  </si>
+  <si>
+    <t>2411</t>
+  </si>
+  <si>
+    <t>2410</t>
+  </si>
+  <si>
+    <t>2409</t>
+  </si>
+  <si>
+    <t>2408</t>
+  </si>
+  <si>
+    <t>2407</t>
+  </si>
+  <si>
+    <t>2406</t>
+  </si>
+  <si>
+    <t>2405</t>
+  </si>
+  <si>
+    <t>2404</t>
+  </si>
+  <si>
+    <t>2403</t>
+  </si>
+  <si>
+    <t>2402</t>
+  </si>
+  <si>
+    <t>2401</t>
+  </si>
+  <si>
+    <t>2312</t>
+  </si>
+  <si>
+    <t>2311</t>
+  </si>
+  <si>
+    <t>2310</t>
+  </si>
+  <si>
+    <t>2309</t>
+  </si>
+  <si>
+    <t>2308</t>
+  </si>
+  <si>
+    <t>2307</t>
+  </si>
+  <si>
+    <t>2306</t>
+  </si>
+  <si>
+    <t>2305</t>
+  </si>
+  <si>
+    <t>2304</t>
+  </si>
+  <si>
+    <t>2303</t>
+  </si>
+  <si>
+    <t>2302</t>
+  </si>
+  <si>
+    <t>2301</t>
+  </si>
+  <si>
+    <t>2212</t>
+  </si>
+  <si>
+    <t>2211</t>
+  </si>
+  <si>
+    <t>2210</t>
+  </si>
+  <si>
+    <t>2209</t>
+  </si>
+  <si>
+    <t>2208</t>
+  </si>
+  <si>
+    <t>2207</t>
+  </si>
+  <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>2111</t>
+  </si>
+  <si>
+    <t>2110</t>
+  </si>
+  <si>
+    <t>2109</t>
+  </si>
+  <si>
+    <t>2108</t>
+  </si>
+  <si>
+    <t>2107</t>
+  </si>
+  <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>2104</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
     <t>1007126904</t>
   </si>
   <si>
     <t>JHON FREDY VILLAR ORTEGA</t>
   </si>
   <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>9299657</t>
-  </si>
-  <si>
-    <t>ORLANDO MARRIAGA MARTINEZ</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>2104</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>2106</t>
-  </si>
-  <si>
-    <t>2107</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>2109</t>
-  </si>
-  <si>
-    <t>2110</t>
-  </si>
-  <si>
-    <t>2111</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>2206</t>
-  </si>
-  <si>
-    <t>2207</t>
-  </si>
-  <si>
-    <t>2208</t>
-  </si>
-  <si>
-    <t>2209</t>
-  </si>
-  <si>
-    <t>2210</t>
-  </si>
-  <si>
-    <t>2211</t>
-  </si>
-  <si>
-    <t>2212</t>
-  </si>
-  <si>
-    <t>2301</t>
-  </si>
-  <si>
-    <t>2302</t>
-  </si>
-  <si>
-    <t>2303</t>
-  </si>
-  <si>
-    <t>2304</t>
-  </si>
-  <si>
-    <t>2305</t>
-  </si>
-  <si>
-    <t>2306</t>
-  </si>
-  <si>
-    <t>2307</t>
-  </si>
-  <si>
-    <t>2308</t>
-  </si>
-  <si>
-    <t>2309</t>
-  </si>
-  <si>
-    <t>2310</t>
-  </si>
-  <si>
-    <t>2311</t>
-  </si>
-  <si>
-    <t>2312</t>
-  </si>
-  <si>
-    <t>2401</t>
-  </si>
-  <si>
-    <t>2402</t>
-  </si>
-  <si>
-    <t>2403</t>
-  </si>
-  <si>
-    <t>2404</t>
-  </si>
-  <si>
-    <t>2405</t>
-  </si>
-  <si>
-    <t>2406</t>
-  </si>
-  <si>
-    <t>2407</t>
-  </si>
-  <si>
-    <t>2408</t>
-  </si>
-  <si>
-    <t>2409</t>
-  </si>
-  <si>
-    <t>2410</t>
-  </si>
-  <si>
-    <t>2411</t>
-  </si>
-  <si>
-    <t>2412</t>
-  </si>
-  <si>
-    <t>2501</t>
+    <t>73125674</t>
+  </si>
+  <si>
+    <t>MELQUI CEDED MORELOS RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>10938491</t>
+  </si>
+  <si>
+    <t>ALFONSO ATENCIO RACERO</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -298,7 +316,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -353,159 +371,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
       </top>
       <bottom style="thin">
         <color indexed="64"/>
@@ -523,6 +391,156 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -568,23 +586,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -612,10 +630,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -653,22 +671,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>496450</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>259200</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97357CEF-F6D3-84ED-4C7F-453BB212434E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A36BD0AA-4AA1-27D0-F0FB-BA08A632486B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -690,7 +708,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="750450" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1019,27 +1037,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C14C7B3-721F-433A-B999-BC5E68438933}">
-  <dimension ref="B2:J81"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00CF6069-B4F1-4BB2-A395-A138C450C531}">
+  <dimension ref="B2:J84"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="16.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1048,7 +1066,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1059,7 +1077,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1070,7 +1088,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1081,10 +1099,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1"/>
-    <row r="7" spans="2:10">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1097,8 +1115,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1"/>
-    <row r="9" spans="2:10">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1113,15 +1131,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1"/>
-    <row r="11" spans="2:10">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>2101687</v>
+        <v>2165918</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1129,17 +1147,17 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1"/>
-    <row r="13" spans="2:10">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C13" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F13" s="5">
         <v>60</v>
@@ -1149,7 +1167,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1169,16 +1187,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1201,7 +1219,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1215,7 +1233,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="18">
-        <v>35112</v>
+        <v>33942</v>
       </c>
       <c r="G17" s="18">
         <v>877803</v>
@@ -1224,7 +1242,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1247,7 +1265,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1270,7 +1288,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1293,7 +1311,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1316,7 +1334,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1339,7 +1357,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1362,7 +1380,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1385,7 +1403,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1408,7 +1426,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1431,7 +1449,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1454,7 +1472,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1477,7 +1495,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1500,7 +1518,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1523,7 +1541,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1546,7 +1564,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1569,7 +1587,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1592,7 +1610,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1615,7 +1633,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1638,7 +1656,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1661,7 +1679,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1684,7 +1702,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1707,7 +1725,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1730,7 +1748,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1753,7 +1771,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1776,7 +1794,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1799,7 +1817,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1822,7 +1840,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1845,7 +1863,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1868,7 +1886,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1891,7 +1909,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1914,7 +1932,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1937,7 +1955,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1960,7 +1978,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -1983,7 +2001,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2006,7 +2024,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2029,7 +2047,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2052,7 +2070,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2075,7 +2093,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2098,7 +2116,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2121,7 +2139,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2144,7 +2162,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2167,7 +2185,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2190,7 +2208,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2213,7 +2231,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2236,7 +2254,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2259,7 +2277,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2282,7 +2300,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2305,7 +2323,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2328,7 +2346,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2351,7 +2369,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2374,7 +2392,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2397,7 +2415,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2420,7 +2438,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2443,7 +2461,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2466,7 +2484,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2489,7 +2507,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2512,7 +2530,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2535,57 +2553,126 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10">
-      <c r="B75" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C75" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D75" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E75" s="22" t="s">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B75" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D75" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="F75" s="24">
-        <v>33942</v>
-      </c>
-      <c r="G75" s="24">
-        <v>877803</v>
-      </c>
-      <c r="H75" s="25"/>
-      <c r="I75" s="25"/>
-      <c r="J75" s="26"/>
-    </row>
-    <row r="80" spans="2:10">
-      <c r="B80" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="C80" s="32"/>
-      <c r="H80" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
-    </row>
-    <row r="81" spans="2:10">
-      <c r="B81" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="C81" s="32"/>
-      <c r="H81" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
+      <c r="F75" s="18">
+        <v>35112</v>
+      </c>
+      <c r="G75" s="18">
+        <v>877803</v>
+      </c>
+      <c r="H75" s="19"/>
+      <c r="I75" s="19"/>
+      <c r="J75" s="20"/>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B76" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D76" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E76" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="18">
+        <v>31249</v>
+      </c>
+      <c r="G76" s="18">
+        <v>828116</v>
+      </c>
+      <c r="H76" s="19"/>
+      <c r="I76" s="19"/>
+      <c r="J76" s="20"/>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B77" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D77" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E77" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F77" s="18">
+        <v>1733</v>
+      </c>
+      <c r="G77" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="20"/>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B78" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D78" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E78" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" s="24">
+        <v>31249</v>
+      </c>
+      <c r="G78" s="24">
+        <v>828116</v>
+      </c>
+      <c r="H78" s="25"/>
+      <c r="I78" s="25"/>
+      <c r="J78" s="26"/>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B83" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C83" s="32"/>
+      <c r="H83" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B84" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C84" s="32"/>
+      <c r="H84" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="H81:J81"/>
-    <mergeCell ref="H80:J80"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="H84:J84"/>
+    <mergeCell ref="H83:J83"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
